--- a/data/trans_orig/P36BPD01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023</t>
+          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>484202</t>
+          <t>483643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>496731</t>
+          <t>497188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>427408</t>
+          <t>426944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>440632</t>
+          <t>440731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>915970</t>
+          <t>916101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>934490</t>
+          <t>934464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>35083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>423867</t>
+          <t>422130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>440834</t>
+          <t>441041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>357673</t>
+          <t>358010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>372564</t>
+          <t>372578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>787573</t>
+          <t>788447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>810066</t>
+          <t>811173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44241</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>631083</t>
+          <t>630903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>659275</t>
+          <t>659031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160361</t>
+          <t>159972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165733</t>
+          <t>165668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>796214</t>
+          <t>796183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>823180</t>
+          <t>823319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35454</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>928764</t>
+          <t>926579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>974643</t>
+          <t>974895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>913572</t>
+          <t>913703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>953321</t>
+          <t>955222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1852436</t>
+          <t>1853223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1920830</t>
+          <t>1923743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102362</t>
+          <t>104547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63201</t>
+          <t>63070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87069</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155463</t>
+          <t>154676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>431423</t>
+          <t>432543</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>453176</t>
+          <t>453214</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>793483</t>
+          <t>792654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>815114</t>
+          <t>815434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1232231</t>
+          <t>1230254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1262832</t>
+          <t>1263866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42626</t>
+          <t>41506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47852</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83153</t>
+          <t>85130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>206462</t>
+          <t>207875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>230658</t>
+          <t>231221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>696079</t>
+          <t>694451</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>723461</t>
+          <t>722170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>915259</t>
+          <t>913105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>950328</t>
+          <t>949089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76144</t>
+          <t>78298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3160774</t>
+          <t>3156498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3235357</t>
+          <t>3232037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3385455</t>
+          <t>3386166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3442148</t>
+          <t>3442193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6554143</t>
+          <t>6560817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6652526</t>
+          <t>6657025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122594</t>
+          <t>125914</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197177</t>
+          <t>201453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129254</t>
+          <t>129209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>185236</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276826</t>
+          <t>272327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>375209</t>
+          <t>368535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>491666</t>
+          <t>532082</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>483643</t>
+          <t>521636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>497188</t>
+          <t>538896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>435777</t>
+          <t>472229</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>426944</t>
+          <t>462644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>440731</t>
+          <t>478717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>927443</t>
+          <t>1004311</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>916101</t>
+          <t>990972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>934464</t>
+          <t>1015374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>25767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>46633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503717</t>
+          <t>549194</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503717</t>
+          <t>549194</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503717</t>
+          <t>549194</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951184</t>
+          <t>1037605</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951184</t>
+          <t>1037605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951184</t>
+          <t>1037605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>434096</t>
+          <t>463270</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422130</t>
+          <t>452339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>441041</t>
+          <t>470986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>366730</t>
+          <t>405782</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>358010</t>
+          <t>396994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>372578</t>
+          <t>412358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>800827</t>
+          <t>869052</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>788447</t>
+          <t>856194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>811173</t>
+          <t>879848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>47028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>449233</t>
+          <t>480079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>449233</t>
+          <t>480079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>449233</t>
+          <t>480079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>831814</t>
+          <t>903222</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>831814</t>
+          <t>903222</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>831814</t>
+          <t>903222</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>646132</t>
+          <t>445285</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>630903</t>
+          <t>435100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>659031</t>
+          <t>453330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>163713</t>
+          <t>182982</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159972</t>
+          <t>178356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165668</t>
+          <t>185802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>809846</t>
+          <t>628267</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>796183</t>
+          <t>616106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>823319</t>
+          <t>637453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>664757</t>
+          <t>468246</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664757</t>
+          <t>468246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>664757</t>
+          <t>468246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655743</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>954392</t>
+          <t>1045121</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>926579</t>
+          <t>1018883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>974895</t>
+          <t>1063507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>930856</t>
+          <t>801375</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>913703</t>
+          <t>785923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>955222</t>
+          <t>813537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1885248</t>
+          <t>1846495</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1853223</t>
+          <t>1817537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1923743</t>
+          <t>1867591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76734</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>64536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>109160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>57647</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>140570</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84156</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154676</t>
+          <t>169528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1031126</t>
+          <t>1128043</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1031126</t>
+          <t>1128043</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1031126</t>
+          <t>1128043</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976773</t>
+          <t>859022</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976773</t>
+          <t>859022</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976773</t>
+          <t>859022</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2007899</t>
+          <t>1987065</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2007899</t>
+          <t>1987065</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2007899</t>
+          <t>1987065</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>443976</t>
+          <t>507505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>432543</t>
+          <t>486808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>453214</t>
+          <t>521153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>804469</t>
+          <t>778699</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>792654</t>
+          <t>765611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>815434</t>
+          <t>789990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1248445</t>
+          <t>1286204</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1230254</t>
+          <t>1265700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1263866</t>
+          <t>1304832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>59471</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41506</t>
+          <t>80168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>52151</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48681</t>
+          <t>65239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>66939</t>
+          <t>111622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>92994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85130</t>
+          <t>132126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315384</t>
+          <t>1397826</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315384</t>
+          <t>1397826</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315384</t>
+          <t>1397826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>223047</t>
+          <t>215735</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>201018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231221</t>
+          <t>224704</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711195</t>
+          <t>787766</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>694451</t>
+          <t>771502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>722170</t>
+          <t>801263</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>934242</t>
+          <t>1003500</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>913105</t>
+          <t>981453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>949089</t>
+          <t>1021568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>31645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>51197</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>37700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61884</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57161</t>
+          <t>68126</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78298</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>235068</t>
+          <t>232663</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235068</t>
+          <t>232663</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>235068</t>
+          <t>232663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>756335</t>
+          <t>838963</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>756335</t>
+          <t>838963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>756335</t>
+          <t>838963</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>991403</t>
+          <t>1071626</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>991403</t>
+          <t>1071626</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>991403</t>
+          <t>1071626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3193311</t>
+          <t>3208998</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3156498</t>
+          <t>3173031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3232037</t>
+          <t>3242254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3412741</t>
+          <t>3428832</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3386166</t>
+          <t>3397675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3442193</t>
+          <t>3453775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6606051</t>
+          <t>6637830</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6560817</t>
+          <t>6592273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6657025</t>
+          <t>6681530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>164640</t>
+          <t>216204</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125914</t>
+          <t>182948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201453</t>
+          <t>252171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>158661</t>
+          <t>199053</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129209</t>
+          <t>174110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185236</t>
+          <t>230210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>323301</t>
+          <t>415257</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272327</t>
+          <t>371557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>368535</t>
+          <t>460814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3357951</t>
+          <t>3425202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3357951</t>
+          <t>3425202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3357951</t>
+          <t>3425202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571402</t>
+          <t>3627885</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571402</t>
+          <t>3627885</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571402</t>
+          <t>3627885</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6929352</t>
+          <t>7053087</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6929352</t>
+          <t>7053087</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6929352</t>
+          <t>7053087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
